--- a/docs/续作排产场景.xlsx
+++ b/docs/续作排产场景.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12180"/>
+    <workbookView windowWidth="28800" windowHeight="12020"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75">
   <si>
     <t>非收尾</t>
   </si>
@@ -206,6 +206,39 @@
   </si>
   <si>
     <t>2、也就是说续作SKU：3302001077 ，在本次排程的月计划日排产量（T~T+2）为0，本次续作SKU不进行排产（如 月生产计划有包含这个SKU,本次续作SKU列入未排），但是机台需要留给其他符合的SKU：3302001078 进行换模排产</t>
+  </si>
+  <si>
+    <t>第七个场景续作：</t>
+  </si>
+  <si>
+    <t>K2024</t>
+  </si>
+  <si>
+    <t>K2025</t>
+  </si>
+  <si>
+    <t>1、由于续作 sku  3302002654  的月计划日排产量为50，班产17，第一天排产出现欠产16，第二天排产不能补上前一天的欠产，所以需要增机台，第一天需上两个机台</t>
+  </si>
+  <si>
+    <t>2、第一天新上的机台：K2025，早班换模、中班开始生产，只生产到16，不需要满班产，因为第一天加上另一个机台生产的34，正好满足月计划日排产量50</t>
+  </si>
+  <si>
+    <t>3、以上这种情况下，SKU：3302002654 在新增排产的排序应该排在所属组的最前面，比如这个SKU是正规组，应该排在正规组的最前面，优先挑选机台</t>
+  </si>
+  <si>
+    <t>第八个场景续作：</t>
+  </si>
+  <si>
+    <t>K1105</t>
+  </si>
+  <si>
+    <t>1、第一天这个续作物料，因为月计划日排产量为0，需要释放机台：K1105 给其他非续作的SKU使用，如果其他SKU没排上这个机台,第二天这个SKU才能续作排这个机台，见以上排程结果</t>
+  </si>
+  <si>
+    <t>2、以上这种情况下释放的这个续作机台：K1105，优先级需要排在新增排产机台排序中最后，降低被选中的概率，这样后续第二天的SKU 3302002546 才能有概率选中这个机台</t>
+  </si>
+  <si>
+    <t>3、如果这个机台第一天被其他SKU安排占用，这个续作SKU因为没有续作机台了，后续只能换模排产，第一天换模，第二天开始排产</t>
   </si>
 </sst>
 </file>
@@ -921,7 +954,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -989,6 +1022,18 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1516,7 +1561,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr/>
-  <dimension ref="A2:O100"/>
+  <dimension ref="A2:O131"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8"/>
   <cols>
     <col min="1" max="1" width="20.5" customWidth="1"/>
@@ -3606,6 +3651,498 @@
         <v>63</v>
       </c>
     </row>
+    <row r="103" spans="1:14">
+      <c r="A103" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B103" s="3"/>
+      <c r="C103" s="3"/>
+      <c r="D103" s="3"/>
+      <c r="E103" s="3"/>
+      <c r="F103" s="3"/>
+      <c r="G103" s="3"/>
+      <c r="H103" s="3"/>
+      <c r="I103" s="3"/>
+      <c r="J103" s="3"/>
+      <c r="K103" s="3"/>
+      <c r="L103" s="3"/>
+      <c r="M103" s="3"/>
+      <c r="N103" s="17"/>
+    </row>
+    <row r="104" spans="1:14">
+      <c r="A104" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="F104" s="16" t="s">
+        <v>1</v>
+      </c>
+      <c r="G104">
+        <f>G107-D111</f>
+        <v>50</v>
+      </c>
+      <c r="I104">
+        <f>I107+G105</f>
+        <v>66</v>
+      </c>
+      <c r="L104">
+        <f>L107+I105</f>
+        <v>65</v>
+      </c>
+      <c r="N104" s="18"/>
+    </row>
+    <row r="105" spans="1:14">
+      <c r="A105" s="5"/>
+      <c r="F105" s="16" t="s">
+        <v>3</v>
+      </c>
+      <c r="G105">
+        <f>G107-G106-D111</f>
+        <v>16</v>
+      </c>
+      <c r="I105">
+        <f>I104-I106</f>
+        <v>15</v>
+      </c>
+      <c r="L105">
+        <f>L104-L106</f>
+        <v>14</v>
+      </c>
+      <c r="N105" s="18"/>
+    </row>
+    <row r="106" spans="1:14">
+      <c r="A106" s="5"/>
+      <c r="F106" s="16" t="s">
+        <v>4</v>
+      </c>
+      <c r="G106">
+        <f>G111+H111</f>
+        <v>34</v>
+      </c>
+      <c r="I106">
+        <f>I111+J111+K111</f>
+        <v>51</v>
+      </c>
+      <c r="L106">
+        <f>L111+M111+N111</f>
+        <v>51</v>
+      </c>
+      <c r="N106" s="18"/>
+    </row>
+    <row r="107" spans="1:14">
+      <c r="A107" s="5"/>
+      <c r="F107" s="16" t="s">
+        <v>6</v>
+      </c>
+      <c r="G107">
+        <v>50</v>
+      </c>
+      <c r="I107">
+        <v>50</v>
+      </c>
+      <c r="L107">
+        <v>50</v>
+      </c>
+      <c r="N107" s="18"/>
+    </row>
+    <row r="108" spans="1:14">
+      <c r="A108" s="5"/>
+      <c r="G108" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="H108" s="7"/>
+      <c r="I108" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="J108" s="7"/>
+      <c r="K108" s="7"/>
+      <c r="L108" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="N108" s="18"/>
+    </row>
+    <row r="109" spans="1:14">
+      <c r="A109" s="5"/>
+      <c r="G109" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="H109" s="7"/>
+      <c r="I109" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="J109" s="7"/>
+      <c r="K109" s="7"/>
+      <c r="L109" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="N109" s="18"/>
+    </row>
+    <row r="110" spans="1:14">
+      <c r="A110" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="B110" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="C110" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="D110" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E110" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="F110" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="G110" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="H110" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="I110" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="J110" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="K110" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="L110" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="M110" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="N110" s="19" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="111" spans="1:14">
+      <c r="A111" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="B111">
+        <v>3302002654</v>
+      </c>
+      <c r="C111">
+        <v>17</v>
+      </c>
+      <c r="D111">
+        <v>0</v>
+      </c>
+      <c r="E111">
+        <v>1500</v>
+      </c>
+      <c r="F111" t="s">
+        <v>24</v>
+      </c>
+      <c r="G111">
+        <v>17</v>
+      </c>
+      <c r="H111">
+        <v>17</v>
+      </c>
+      <c r="I111">
+        <v>17</v>
+      </c>
+      <c r="J111">
+        <v>17</v>
+      </c>
+      <c r="K111">
+        <v>17</v>
+      </c>
+      <c r="L111">
+        <v>17</v>
+      </c>
+      <c r="M111">
+        <v>17</v>
+      </c>
+      <c r="N111" s="25">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="112" spans="1:14">
+      <c r="A112" s="12" t="s">
+        <v>66</v>
+      </c>
+      <c r="B112" s="23">
+        <v>3302002654</v>
+      </c>
+      <c r="C112" s="23">
+        <v>17</v>
+      </c>
+      <c r="D112" s="23">
+        <v>0</v>
+      </c>
+      <c r="E112" s="23">
+        <v>1500</v>
+      </c>
+      <c r="F112" s="23" t="s">
+        <v>54</v>
+      </c>
+      <c r="G112" s="13"/>
+      <c r="H112" s="13">
+        <v>16</v>
+      </c>
+      <c r="I112" s="13"/>
+      <c r="J112" s="13"/>
+      <c r="K112" s="13"/>
+      <c r="L112" s="13"/>
+      <c r="M112" s="13"/>
+      <c r="N112" s="22"/>
+    </row>
+    <row r="113" spans="1:1">
+      <c r="A113" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="114" spans="1:1">
+      <c r="A114" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="115" spans="1:1">
+      <c r="A115" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="116" spans="1:1">
+      <c r="A116" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="119" spans="1:14">
+      <c r="A119" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B119" s="3"/>
+      <c r="C119" s="3"/>
+      <c r="D119" s="3"/>
+      <c r="E119" s="3"/>
+      <c r="F119" s="3"/>
+      <c r="G119" s="3"/>
+      <c r="H119" s="3"/>
+      <c r="I119" s="3"/>
+      <c r="J119" s="3"/>
+      <c r="K119" s="3"/>
+      <c r="L119" s="3"/>
+      <c r="M119" s="3"/>
+      <c r="N119" s="17"/>
+    </row>
+    <row r="120" spans="1:14">
+      <c r="A120" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="F120" s="16" t="s">
+        <v>1</v>
+      </c>
+      <c r="G120">
+        <f>G123-D127</f>
+        <v>0</v>
+      </c>
+      <c r="I120">
+        <f>I123+G121</f>
+        <v>32</v>
+      </c>
+      <c r="L120">
+        <f>L123+I121</f>
+        <v>31</v>
+      </c>
+      <c r="N120" s="18"/>
+    </row>
+    <row r="121" spans="1:14">
+      <c r="A121" s="5"/>
+      <c r="F121" s="16" t="s">
+        <v>3</v>
+      </c>
+      <c r="G121">
+        <f>G123-G122-D127</f>
+        <v>0</v>
+      </c>
+      <c r="I121">
+        <f>I120-I122</f>
+        <v>-19</v>
+      </c>
+      <c r="L121">
+        <f>L120-L122</f>
+        <v>-20</v>
+      </c>
+      <c r="N121" s="18"/>
+    </row>
+    <row r="122" spans="1:14">
+      <c r="A122" s="5"/>
+      <c r="F122" s="16" t="s">
+        <v>4</v>
+      </c>
+      <c r="G122">
+        <f>G127+H127</f>
+        <v>0</v>
+      </c>
+      <c r="I122">
+        <f>I127+J127+K127</f>
+        <v>51</v>
+      </c>
+      <c r="L122">
+        <f>L127+M127+N127</f>
+        <v>51</v>
+      </c>
+      <c r="N122" s="18"/>
+    </row>
+    <row r="123" spans="1:14">
+      <c r="A123" s="5"/>
+      <c r="F123" s="16" t="s">
+        <v>6</v>
+      </c>
+      <c r="G123">
+        <v>0</v>
+      </c>
+      <c r="I123">
+        <v>32</v>
+      </c>
+      <c r="L123">
+        <v>50</v>
+      </c>
+      <c r="N123" s="18"/>
+    </row>
+    <row r="124" spans="1:14">
+      <c r="A124" s="5"/>
+      <c r="G124" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="H124" s="7"/>
+      <c r="I124" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="J124" s="7"/>
+      <c r="K124" s="7"/>
+      <c r="L124" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="N124" s="18"/>
+    </row>
+    <row r="125" spans="1:14">
+      <c r="A125" s="5"/>
+      <c r="G125" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="H125" s="7"/>
+      <c r="I125" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="J125" s="7"/>
+      <c r="K125" s="7"/>
+      <c r="L125" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="N125" s="18"/>
+    </row>
+    <row r="126" spans="1:14">
+      <c r="A126" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="B126" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="C126" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="D126" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E126" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="F126" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="G126" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="H126" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="I126" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="J126" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="K126" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="L126" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="M126" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="N126" s="19" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="127" spans="1:14">
+      <c r="A127" s="11" t="s">
+        <v>71</v>
+      </c>
+      <c r="B127" s="1">
+        <v>3302002546</v>
+      </c>
+      <c r="C127" s="1">
+        <v>17</v>
+      </c>
+      <c r="D127" s="1">
+        <v>0</v>
+      </c>
+      <c r="E127" s="1">
+        <v>1732</v>
+      </c>
+      <c r="F127" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="G127" s="1"/>
+      <c r="H127" s="1"/>
+      <c r="I127" s="1">
+        <v>17</v>
+      </c>
+      <c r="J127" s="1">
+        <v>17</v>
+      </c>
+      <c r="K127" s="1">
+        <v>17</v>
+      </c>
+      <c r="L127" s="1">
+        <v>17</v>
+      </c>
+      <c r="M127" s="1">
+        <v>17</v>
+      </c>
+      <c r="N127" s="26">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="128" ht="17" spans="1:1">
+      <c r="A128" s="24" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="129" spans="1:1">
+      <c r="A129" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="130" spans="1:1">
+      <c r="A130" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="131" spans="1:1">
+      <c r="A131" t="s">
+        <v>74</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
